--- a/open_agentic/capsuled_data_prep/kb/Coffee/internet.xlsx
+++ b/open_agentic/capsuled_data_prep/kb/Coffee/internet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,36 +456,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brown_Eye_Spot</t>
+          <t>Miner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mycosphaerella coffeicola</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
+          <t>Leucoptera sp.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Foliar, Pod, Stem</t>
+          <t>Foliar, Whole plant</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Small brown spots on leaves with light brown or grey centres surrounded by dark brown rings and yellow margins, growing up to 15 mm diameter. Smaller irregular brown spots on berries, less than 5 mm wide.. Circular brown spots mostly 5-10 mm with bright grey centres and yellow haloes; characteristic appearance with light brown or grey centers, dark brown outer ring, and yellow margins. Colletotrichum gloeosporioides</t>
+          <t>Irregular brown spots on the upper leaf surface, pale yellow trails under the leaf epidermis, and large necrotic patches caused by larval mining of the mesophyll.. Mines formed by larvae visible as pale yellow trails under the leaf epidermis, developing into large necrotic patches; larvae transparent and up to 3.5 mm in length found within mines; silk X-shaped cocoons in the axial region of the leaf.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +490,159 @@
           <t>Rust</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hemileia vastatrix</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Foliar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Large orange spots on the undersides of leaves, premature leaf fall, and characteristic yellow spots on the undersurface of leaves caused by spores erupting through stomata.. Characteristic yellow spots on the undersurface of leaves caused by uredinia containing new spores that erupt through stomata; orange spots appear on the undersides of leaves.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Berry_Blotch</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cercospora coffeicola</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Foliar, Seed, Stem</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Small brown circular spots on leaves up to 15 mm diameter with light brown or grey centres, dark brown rings, and yellow margins; brown irregular spots on berries, sometimes covering the whole berry; young fruit tend to ripen prematurely.. Circular spots with light brown or grey centres surrounded by a wide dark brown ring and yellow margin on leaves; on berries, spots are smaller, more irregular in shape, and mainly on the sun-exposed side; premature ripening of young fruit.. Sunburn</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Black_Rot</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Koleroga noxia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Pod</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dark brown or black decaying leaves, twigs, and berries; dead leaves and berries remain attached to branches held by white web-like fungal mycelial threads visible on twigs and petioles; sclerotia visible over affected areas; defoliation and fruit drop occur.. White, web-like fungal threads (mycelium) visible on twigs and petioles, holding dead leaves and berries attached to branches instead of falling; sclerotia (resting bodies) scattered over affected areas.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brown_Eye_Spot</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cerscospora</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Phoma</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/open_agentic/capsuled_data_prep/kb/Coffee/internet.xlsx
+++ b/open_agentic/capsuled_data_prep/kb/Coffee/internet.xlsx
@@ -456,43 +456,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Miner</t>
+          <t>Brown_Eye_Spot</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leucoptera sp.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Cercospora coffeicola</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Foliar, Whole plant</t>
+          <t>Foliar, Seed, Stem</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Irregular brown spots on the upper leaf surface, pale yellow trails under the leaf epidermis, and large necrotic patches caused by larval mining of the mesophyll.. Mines formed by larvae visible as pale yellow trails under the leaf epidermis, developing into large necrotic patches; larvae transparent and up to 3.5 mm in length found within mines; silk X-shaped cocoons in the axial region of the leaf.</t>
+          <t>Small brown circular spots on leaves up to 15 mm diameter with light brown or grey centres, dark brown rings, and yellow margins; on berries, smaller irregular brown spots mainly on sun-exposed side.. Circular spots with bright grey centres, dark brown ring border, and yellow haloes on leaves; spots occur mostly between the veins; spore masses visible in grey centres; on berries spots are irregular, brown, and mainly on the sun-exposed side.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Black_Rot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hemileia vastatrix</t>
+          <t>Pellicularia koleroga</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,67 +506,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Foliar</t>
+          <t>Foliar, Stem</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Large orange spots on the undersides of leaves, premature leaf fall, and characteristic yellow spots on the undersurface of leaves caused by spores erupting through stomata.. Characteristic yellow spots on the undersurface of leaves caused by uredinia containing new spores that erupt through stomata; orange spots appear on the undersides of leaves.</t>
+          <t>The fungus forms mats and threads of light-coloured growth on the underside of leaves and twigs. Leaves appear light grey and dry at first, then blacken and fall; dead leaves are held in place by fungal threads. Dark brown or black decaying leaves, twigs and berries; defoliation and fruit drop observed.. White thread-like strands forming webs over the underside of leaves; black threads holding detached dead leaves on branches; mycelial threads (fungal strands) visible on twigs and petioles; sclerotia visible all over affected areas.. White thread blight (Marasmiellus scandens), Horse hair blight (Marasmius crinis-equi)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Berry_Blotch</t>
+          <t>Miner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cercospora coffeicola</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fungal</t>
+          <t>Leucoptera sp.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Foliar, Seed, Stem</t>
+          <t>Foliar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Small brown circular spots on leaves up to 15 mm diameter with light brown or grey centres, dark brown rings, and yellow margins; brown irregular spots on berries, sometimes covering the whole berry; young fruit tend to ripen prematurely.. Circular spots with light brown or grey centres surrounded by a wide dark brown ring and yellow margin on leaves; on berries, spots are smaller, more irregular in shape, and mainly on the sun-exposed side; premature ripening of young fruit.. Sunburn</t>
+          <t>Irregular brown spots on the upper leaf surface, pale yellow trails (mines) under the leaf epidermis, and large necrotic patches caused by larval mining.. Pale yellow trails (mines) visible under the leaf epidermis that develop into large necrotic patches; larvae present in the mines feeding on the mesophyll; irregular brown spots on the upper leaf surface.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Black_Rot</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Koleroga noxia</t>
+          <t>Hemileia vastatrix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,17 +571,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Pod</t>
+          <t>Foliar, Whole plant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dark brown or black decaying leaves, twigs, and berries; dead leaves and berries remain attached to branches held by white web-like fungal mycelial threads visible on twigs and petioles; sclerotia visible over affected areas; defoliation and fruit drop occur.. White, web-like fungal threads (mycelium) visible on twigs and petioles, holding dead leaves and berries attached to branches instead of falling; sclerotia (resting bodies) scattered over affected areas.</t>
+          <t>Irregular shaped spots on upper leaf surfaces connected with yellow to orange powdery lesions on the lower leaf surfaces where the spores are located. Leaves eventually dry up and turn brown. Infected trees may prematurely drop infected leaves resulting in long, bare branches. Large orange/yellow spots on the undersides of leaves lead to premature leaf fall.. Yellow to orange powdery lesions on the lower leaf surface containing rust spores (uredinia erupting through stomata); spots mostly begin at leaf edges or tips where water collects; first lesions appear on lowermost leaves and infection progresses upward into the tree.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -592,51 +591,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brown_Eye_Spot</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>Phoma</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Phoma tarda</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Foliar, Stem</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Produces circular dark-colored spots of varying sizes on leaves (up to 2 cm diameter), dark depressed lesions on branches (dry shoots), and necrosis of flowers and fruits. Leaves may curve and crack at edges.. Circular dark-colored spots of varying sizes on leaves up to 2 cm in diameter; dark depressed lesions on branches that can involve the entire diameter (dry shoots); infection begins at the apical part in the terminal shoot and tender leaves; leaves curve and may present cracks when lesions reach edges.. boron deficiency</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cerscospora</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>Berry_Blotch</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cercospora coffeicola</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Foliar, Seed, Stem</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Small brown circular spots on leaves up to 15 mm diameter with light brown or grey centres, dark brown rings, and yellow margins; brown irregular spots on berries, sometimes covering the whole berry; young fruit tend to ripen prematurely.. Circular spots with light brown or grey centres surrounded by a wide dark brown ring and yellow margin on leaves; on berries, spots are smaller, more irregular in shape, and mainly on the sun-exposed side; premature ripening of young fruit.. Sunburn</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Phoma</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>Cerscospora</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>low</t>
